--- a/教育訓練教材/backend/chat_logs.xlsx
+++ b/教育訓練教材/backend/chat_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +497,32 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-06 15:17:48</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1.一階調撥.md</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>是否能幫我美化圖片</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>學員您好！
+很抱歉，我是企業內訓的 AI 助教，目前主要協助解答內部訓練教材相關的問題（例如：ERP 倉儲單據作業流程、三合一對刷系統操作、迎新與公司規範等）。
+由於**「圖片美化」**不在本次的教材與系統服務範圍內，我無法直接幫您修圖或美化圖片。建議您可以使用專門的影像處理軟體或圖片編輯工具來進行處理。
+如果您在閱讀教材或操作內部系統時有任何疑問，隨時歡迎向我提問，我很樂意為您解答！
+*(Powered by gemini-3.8-flash / Key: AQ.A...wlGw)*</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/教育訓練教材/backend/chat_logs.xlsx
+++ b/教育訓練教材/backend/chat_logs.xlsx
@@ -2,27 +2,33 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="3"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -50,7 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +419,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <cols>
+    <col width="20" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="15.5703125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.28515625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="255.7109375" bestFit="1" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -523,6 +535,178 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:02:37</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>01_新手指南.md</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>請用一句話介紹你自己</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>您好！我是您的專業企業內訓 AI 助教，隨時準備根據您的教材內容，提供專業且親切的學習支援與疑問解答。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:02:46</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01_新手指南.md</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>你好，請用繁體中文回覆一句話</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>您好！很樂意為您服務，這是一句繁體中文的回覆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:19:24</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>T100-N系列廠間調撥操作.md</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>請購單要注意什麼</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>您好！非常樂意為您說明「請購單」的注意事項。
+根據您提及的「請購單」，這主要涉及到我們的【14.請購單維護】教材內容，與您目前研讀的【T100-N系列廠間調撥操作】雖然是不同的作業，但在系統操作邏輯上有一些共通之處。
+「請購單」是企業內發起物料或服務採購需求的重要單據。以下是您在處理請購單時需要特別留意的重點：
+### 請購單的關鍵注意事項
+1.  **目的明確與需求確認：**
+    *   **為什麼要請購？** 在建立請購單前，請務必確認請購的物料或服務是因應生產、維修、行政等實際需求，並與相關單位進行需求確認。
+    *   **避免重複請購：** 確認倉庫是否有現有庫存或是否有其他請購單正在處理相同需求。
+2.  **資訊正確性與完整性：**
+    *   **料號/服務項目：** 務必填寫正確的料號或詳細的服務描述，避免後續採購錯誤。
+    *   **規格：** 如果有規格需求，例如尺寸、材質、顏色等，務必清楚註明。
+    *   **數量：** 精確計算所需數量，避免過多或不足，可參考類似「廠間調撥」中計算機精確計算數量的做法。
+    *   **需求日期：** 明確指出物料或服務的預期到貨/完成日期，以利採購單位安排。
+    *   **用途/備註：** 在備註欄位詳細說明請購目的，例如「用於X生產線」，以利採購人員理解需求。
+3.  **單據流程與權責：**
+    *   **核准權限：** 確認請購單是否需經過相關主管的審核與核准，確保符合公司的採購政策。
+    *   **單據類型：** 如果系統有多種請購單類型（例如：一般請購、急件請購），請選擇正確的類型。
+### 請購單的簡易操作步驟要點 (參考【14.請購單維護】教材摘要)
+由於【14.請購單維護】教材摘要中僅簡要提及「步驟 1 一、物料請購」，我們可以推斷其核心流程應包含以下要點：
+1.  **進入請購單維護作業：** 在系統主畫面中找到並點擊「請購單維護」或類似的作業圖示。
+2.  **新增請購單：** 點擊「新增」按鈕（通常為帶有「+」號的白色文件圖示）。
+3.  **填寫單頭資訊：** 輸入請購日期、請購部門、請購人員等基本資訊。
+4.  **新增明細項目：** 在明細區塊點擊「新增」按鈕，輸入或查詢所需的「料號」、「規格」、「數量」以及「需求日期」等資訊。
+5.  **存檔與送審：** 完成資料輸入後，點擊「存檔」按鈕，並依公司流程將請購單送交相關主管進行「稽核」或「審核」。
+請購單的正確填寫與流程遵循，是確保物料供應順暢、成本有效控制的重要環節。若您在操作時遇到任何具體問題，或是想了解更多關於請購單的細節，請隨時提出，我會再為您提供更詳細的協助！</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:26:27</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.一階調撥.md</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>物料請購</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>您好！很高興為您解答關於「物料請購」的問題。
+您目前正在研讀的【1.一階調撥】教材主要介紹的是倉庫內部或廠區間的物料調撥流程。而您詢問的「物料請購」，則是公司在需要採購新物料時所進行的流程，這部分更詳細的說明可以在【14.請購單維護】教材中找到。
+以下是根據相關教材【14.請購單維護】所整理的「物料請購」流程要點：
+### 物料請購流程要點
+1.  **目的**：當公司有物料需求時，透過請購單記錄所需物料的種類與數量，啟動後續的採購作業。
+2.  **操作步驟**：
+    *   **步驟 1：物料請購**
+        *   這是整個請購流程的起始點，相關人員會在此步驟提出所需的物料清單。
+        *   (教材圖片顯示一個系統介面，上面有物料請購的相關欄位，但未提供具體點擊按鈕或輸入內容的文字說明，故在此處僅能概述其為請購作業的起始介面。)
+    *   **步驟 2：繕繕發包申請單**
+        *   在物料請購完成後，系統可能會根據請購內容，進行下一步的「繕繕發包申請單」作業，這通常牽涉到將請購需求轉化為對供應商的發包或採購申請。
+        *   (教材圖片顯示一個發包申請單的介面，同樣未提供具體操作細節，因此以功能概述為主。)
+總結來說，「物料請購」是透過系統填寫和維護請購單，確保公司各部門的物料需求能夠被記錄並啟動後續採購流程的重要環節。如果您想深入了解請購單的具體操作細節，建議您可以參考【14.請購單維護】教材的完整內容。
+希望這個回答對您有幫助！如果您還有其他問題，歡迎隨時提出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-07 14:22:30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.一階調撥.md</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>批號</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>您好！感謝您的提問，批號 (Batch number) 在我們的倉儲管理中是一個非常重要的概念。雖然您目前研讀的《1.一階調撥》教材主要聚焦於調撥單的建立步驟，但批號是執行調撥作業前不可或缺的前置資訊。
+根據相關教材，我將為您統整關於「批號」的說明如下：
+---
+### **1. 批號的定義與目的**
+*   **定義：** 批號是系統用來識別和追蹤特定批次料件或產品的唯一編號。它通常與該批次的生產日期、特性、品質檢驗結果或來源等資訊相關聯。
+*   **目的：**
+    *   **精準追溯：** 確保在需要追溯時，能快速找出特定批次的產品資訊，例如品質異常追查。
+    *   **庫存管理：** 協助管理不同批次的庫存，特別是在有先進先出 (FIFO) 或批次管理需求的料件上。
+    *   **調撥準確性：** 確保在進行料件調撥時，能夠正確選擇並記錄要移動的特定批次。
+### **2. 與「一階調撥」的關聯性**
+*   您目前學習的《1.一階調撥》教材，教導您如何在系統中新增調撥單並輸入數量。然而，在執行這些步驟之前，您需要先知道要調撥的是哪一個「批號」的料件。
+*   根據**《T100-N系列廠間調撥操作》**教材的核心重點，在建立任何調撥單（包括一階調撥）時，必須：
+    *   透過內部訊息管道（例如 LINE）先行取得確切的「批號」。
+    *   利用系統中的「庫存明細查詢作業」，確認該批號的庫存狀況與相關資料（如料號、規格），以確保後續調撥的準確性。
+*   簡單來說，雖然《1.一階調撥》教材沒有直接顯示「輸入批號」的欄位，但「確認正確批號」是您能正確填寫「調撥數量」的前提準備工作。
+### **3. 批號的維護與管理**
+*   批號的相關資訊（如製造日期、備註等）可以在 T100 系統的「**批號維護作業 (aimi715)**」中進行修改。
+*   根據**《批號維護作業(修改製造日期、備註)》**教材的說明：
+    *   **資訊核對精準度：** 在執行批號維護前，務必先確認工單完工入庫單或庫存報表上的「料件編號」與「批號」，以避免更正錯誤的批次。
+    *   **連動欄位檢視：** 在修改批號單身中的「製造日期」後，也需留意是否有其他連動欄位需要同步確認或調整。
+### **重點整理與操作建議：**
+1.  **確認批號：** 在進行任何調撥作業（包括一階調撥）前，請務必向倉庫人員或相關部門確認欲調撥料件的正確「批號」。
+2.  **查詢庫存：** 善用系統的「庫存明細查詢作業」功能，核對該批號的庫存量與詳細資訊，確保調撥數據正確無誤。
+3.  **建立調撥單：** 依據確認的批號與數量，按照《1.一階調撥》教材的步驟，在系統中輸入調撥數量。
+4.  **批號資訊維護：** 若發現批號的製造日期或備註有誤，請依循《批號維護作業》教材，使用 T100 系統的 **aimi715 批號維護作業** 進行更正。
+---
+希望這樣的說明能幫助您更全面地理解「批號」在倉儲作業中的應用。如果您還有其他問題，或想進一步了解批號相關的操作細節，都歡迎隨時提出！</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/教育訓練教材/backend/chat_logs.xlsx
+++ b/教育訓練教材/backend/chat_logs.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="20" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -707,6 +707,57 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-08 14:29:34</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.一階調撥.md</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>調撥</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>您好！關於「調撥」的流程，我為您整理了當前研讀教材《1.一階調撥》以及相關教材《T100-N系列廠間調撥操作》的重點，讓您對調撥作業有更全面的了解。
+---
+**一、 什麼是調撥？**
+「調撥」指的是將貨物或庫存從一個地點（例如倉庫）轉移到另一個地點的作業。這在倉儲管理中是常見的，確保不同地點的庫存能有效流通與供應。
+---
+**二、 一階調撥作業流程 (根據《1.一階調撥.md》)**
+這份教材主要說明了在系統中執行基礎調撥的三個主要步驟：
+1.  **新增調撥單據**：
+    *   點擊「+ 新增」按鈕。
+    *   在下拉式選單中選擇正確的「單據別編號」。
+2.  **輸入調撥數量**：
+    *   根據倉庫人員提供的實際調撥數量。
+    *   在單身部分的指定欄位（如下圖打勾處）鍵入數量。
+3.  **列印單據**：
+    *   將完成的調撥單據列印出來。
+    *   提供給地磅人員進行後續的磅重與核對作業。
+---
+**三、 廠間調撥的補充資訊與注意事項 (根據《T100-N系列廠間調撥操作.md》)**
+這份教材針對N系列產品的「廠間調撥」提供了更細緻的指引，強調了資訊確認與關鍵欄位的填寫：
+1.  **資訊先行與確認**：
+    *   **取得批號**：在建立調撥單前，務必先透過 LINE 訊息取得確切的「批號」。
+    *   **確認庫存**：利用「庫存明細查詢作業」確認該批號的庫存狀況、料號、規格等相關資料，以確保調撥的準確性。
+2.  **調撥單關鍵欄位填寫**：
+    *   **調撥日期**：請務必正確填寫。如是次日才進行調撥，需提前調整日期。
+    *   **調撥單號 (來源)**：選擇「IN201」。
+    *   **車牌號碼**：詳細輸入載運貨物的「車牌號碼」。
+---
+**總結**
+「一階調撥」主要聚焦在系統操作的基礎步驟，而「T100-N系列廠間調撥操作」則進一步補充了調撥前的資訊核對和重要欄位的填寫細節，兩者都是確保調撥作業順暢、正確的關鍵。
+希望這些資訊能幫助您更好地理解調撥的相關作業！如果您還有其他問題，歡迎隨時提出喔！</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
